--- a/scripts/guardian-imports/provisioning/inputs/guardian-provisioning.xlsx
+++ b/scripts/guardian-imports/provisioning/inputs/guardian-provisioning.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\edu-affairs-v2\scripts\guardian-imports\provisioning\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B88A0730-994A-4CB2-A5BE-ABBC0F36F6FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{777C48DA-E3F1-4182-B4DA-BF4AA09F265E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15450" yWindow="2850" windowWidth="12060" windowHeight="8190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16545" yWindow="2820" windowWidth="12180" windowHeight="6765" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="guardian-provisioning" sheetId="1" r:id="rId1"/>
+    <sheet name="guardian-provisioning (2)" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="15">
   <si>
     <t>displayName</t>
   </si>
@@ -64,13 +65,19 @@
   </si>
   <si>
     <t>حصه محمد الفهد</t>
+  </si>
+  <si>
+    <t>ربى سليمان عبدالرحمن الطوالة</t>
+  </si>
+  <si>
+    <t>r.altwala@qz.org.sa</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -85,6 +92,11 @@
     </font>
     <font>
       <sz val="9"/>
+      <color theme="1"/>
+      <name val="Tajawal"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Tajawal"/>
     </font>
@@ -115,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -129,6 +141,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -409,6 +422,58 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="30.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.5703125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.5703125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.7109375" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="5">
+        <v>1093648168</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="5">
+        <v>567187167</v>
+      </c>
+      <c r="E2" s="5">
+        <v>1093648168</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FEEB7AC-7F28-4B32-B3FB-CFDA744CDFFA}">
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -507,7 +572,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C3" r:id="rId1" xr:uid="{EE6C92D1-E9E1-445F-8AA5-F43B02F729AF}"/>
+    <hyperlink ref="C3" r:id="rId1" xr:uid="{B0E678EF-FCD7-48C5-B660-87171A61A71F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
